--- a/e2e-screenshots/reports-insights-panels/fixtures/VELOCITY_SALES.xlsx
+++ b/e2e-screenshots/reports-insights-panels/fixtures/VELOCITY_SALES.xlsx
@@ -461,7 +461,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-07-27</v>
+        <v>2026-08-02</v>
       </c>
       <c r="B2" t="str">
         <v>AMZ-FM-6001</v>
@@ -517,7 +517,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-07-27</v>
+        <v>2026-08-02</v>
       </c>
       <c r="B3" t="str">
         <v>AMZ-FM-6002</v>
@@ -573,7 +573,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-07-27</v>
+        <v>2026-08-02</v>
       </c>
       <c r="B4" t="str">
         <v>AMZ-RA-6010</v>
@@ -629,7 +629,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026-07-27</v>
+        <v>2026-08-02</v>
       </c>
       <c r="B5" t="str">
         <v>AMZ-RA-6011</v>
@@ -685,7 +685,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-07-27</v>
+        <v>2026-08-02</v>
       </c>
       <c r="B6" t="str">
         <v>AMZ-RA-6012</v>
@@ -741,7 +741,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-07-27</v>
+        <v>2026-08-02</v>
       </c>
       <c r="B7" t="str">
         <v>AMZ-RA-6013</v>
@@ -864,7 +864,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-07-27</v>
+        <v>2026-08-02</v>
       </c>
       <c r="B2" t="str">
         <v>EBAY-SM-6006</v>
@@ -920,7 +920,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-07-27</v>
+        <v>2026-08-02</v>
       </c>
       <c r="B3" t="str">
         <v>EBAY-SM-6007</v>

--- a/e2e-screenshots/reports-insights-panels/fixtures/VELOCITY_SALES.xlsx
+++ b/e2e-screenshots/reports-insights-panels/fixtures/VELOCITY_SALES.xlsx
@@ -461,7 +461,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-08-02</v>
+        <v>2026-08-05</v>
       </c>
       <c r="B2" t="str">
         <v>AMZ-FM-6001</v>
@@ -517,7 +517,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-08-02</v>
+        <v>2026-08-05</v>
       </c>
       <c r="B3" t="str">
         <v>AMZ-FM-6002</v>
@@ -573,7 +573,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-08-02</v>
+        <v>2026-08-05</v>
       </c>
       <c r="B4" t="str">
         <v>AMZ-RA-6010</v>
@@ -629,7 +629,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026-08-02</v>
+        <v>2026-08-05</v>
       </c>
       <c r="B5" t="str">
         <v>AMZ-RA-6011</v>
@@ -685,7 +685,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-08-02</v>
+        <v>2026-08-05</v>
       </c>
       <c r="B6" t="str">
         <v>AMZ-RA-6012</v>
@@ -741,7 +741,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-08-02</v>
+        <v>2026-08-05</v>
       </c>
       <c r="B7" t="str">
         <v>AMZ-RA-6013</v>
@@ -864,7 +864,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-08-02</v>
+        <v>2026-08-05</v>
       </c>
       <c r="B2" t="str">
         <v>EBAY-SM-6006</v>
@@ -920,7 +920,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-08-02</v>
+        <v>2026-08-05</v>
       </c>
       <c r="B3" t="str">
         <v>EBAY-SM-6007</v>

--- a/e2e-screenshots/reports-insights-panels/fixtures/VELOCITY_SALES.xlsx
+++ b/e2e-screenshots/reports-insights-panels/fixtures/VELOCITY_SALES.xlsx
@@ -461,7 +461,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-08-05</v>
+        <v>2026-08-06</v>
       </c>
       <c r="B2" t="str">
         <v>AMZ-FM-6001</v>
@@ -517,7 +517,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-08-05</v>
+        <v>2026-08-06</v>
       </c>
       <c r="B3" t="str">
         <v>AMZ-FM-6002</v>
@@ -573,7 +573,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-08-05</v>
+        <v>2026-08-06</v>
       </c>
       <c r="B4" t="str">
         <v>AMZ-RA-6010</v>
@@ -629,7 +629,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026-08-05</v>
+        <v>2026-08-06</v>
       </c>
       <c r="B5" t="str">
         <v>AMZ-RA-6011</v>
@@ -685,7 +685,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-08-05</v>
+        <v>2026-08-06</v>
       </c>
       <c r="B6" t="str">
         <v>AMZ-RA-6012</v>
@@ -741,7 +741,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-08-05</v>
+        <v>2026-08-06</v>
       </c>
       <c r="B7" t="str">
         <v>AMZ-RA-6013</v>
@@ -864,7 +864,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-08-05</v>
+        <v>2026-08-06</v>
       </c>
       <c r="B2" t="str">
         <v>EBAY-SM-6006</v>
@@ -920,7 +920,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-08-05</v>
+        <v>2026-08-06</v>
       </c>
       <c r="B3" t="str">
         <v>EBAY-SM-6007</v>

--- a/e2e-screenshots/reports-insights-panels/fixtures/VELOCITY_SALES.xlsx
+++ b/e2e-screenshots/reports-insights-panels/fixtures/VELOCITY_SALES.xlsx
@@ -461,7 +461,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-08-06</v>
+        <v>2026-08-07</v>
       </c>
       <c r="B2" t="str">
         <v>AMZ-FM-6001</v>
@@ -517,7 +517,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-08-06</v>
+        <v>2026-08-07</v>
       </c>
       <c r="B3" t="str">
         <v>AMZ-FM-6002</v>
@@ -573,7 +573,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-08-06</v>
+        <v>2026-08-07</v>
       </c>
       <c r="B4" t="str">
         <v>AMZ-RA-6010</v>
@@ -629,7 +629,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026-08-06</v>
+        <v>2026-08-07</v>
       </c>
       <c r="B5" t="str">
         <v>AMZ-RA-6011</v>
@@ -685,7 +685,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-08-06</v>
+        <v>2026-08-07</v>
       </c>
       <c r="B6" t="str">
         <v>AMZ-RA-6012</v>
@@ -741,7 +741,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-08-06</v>
+        <v>2026-08-07</v>
       </c>
       <c r="B7" t="str">
         <v>AMZ-RA-6013</v>
@@ -864,7 +864,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-08-06</v>
+        <v>2026-08-07</v>
       </c>
       <c r="B2" t="str">
         <v>EBAY-SM-6006</v>
@@ -920,7 +920,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-08-06</v>
+        <v>2026-08-07</v>
       </c>
       <c r="B3" t="str">
         <v>EBAY-SM-6007</v>

--- a/e2e-screenshots/reports-insights-panels/fixtures/VELOCITY_SALES.xlsx
+++ b/e2e-screenshots/reports-insights-panels/fixtures/VELOCITY_SALES.xlsx
@@ -461,7 +461,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-08-07</v>
+        <v>2026-08-08</v>
       </c>
       <c r="B2" t="str">
         <v>AMZ-FM-6001</v>
@@ -517,7 +517,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-08-07</v>
+        <v>2026-08-08</v>
       </c>
       <c r="B3" t="str">
         <v>AMZ-FM-6002</v>
@@ -573,7 +573,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-08-07</v>
+        <v>2026-08-08</v>
       </c>
       <c r="B4" t="str">
         <v>AMZ-RA-6010</v>
@@ -629,7 +629,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026-08-07</v>
+        <v>2026-08-08</v>
       </c>
       <c r="B5" t="str">
         <v>AMZ-RA-6011</v>
@@ -685,7 +685,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-08-07</v>
+        <v>2026-08-08</v>
       </c>
       <c r="B6" t="str">
         <v>AMZ-RA-6012</v>
@@ -741,7 +741,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-08-07</v>
+        <v>2026-08-08</v>
       </c>
       <c r="B7" t="str">
         <v>AMZ-RA-6013</v>
@@ -864,7 +864,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-08-07</v>
+        <v>2026-08-08</v>
       </c>
       <c r="B2" t="str">
         <v>EBAY-SM-6006</v>
@@ -920,7 +920,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-08-07</v>
+        <v>2026-08-08</v>
       </c>
       <c r="B3" t="str">
         <v>EBAY-SM-6007</v>

--- a/e2e-screenshots/reports-insights-panels/fixtures/VELOCITY_SALES.xlsx
+++ b/e2e-screenshots/reports-insights-panels/fixtures/VELOCITY_SALES.xlsx
@@ -461,7 +461,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-08-08</v>
+        <v>2026-08-11</v>
       </c>
       <c r="B2" t="str">
         <v>AMZ-FM-6001</v>
@@ -517,7 +517,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-08-08</v>
+        <v>2026-08-11</v>
       </c>
       <c r="B3" t="str">
         <v>AMZ-FM-6002</v>
@@ -573,7 +573,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-08-08</v>
+        <v>2026-08-11</v>
       </c>
       <c r="B4" t="str">
         <v>AMZ-RA-6010</v>
@@ -629,7 +629,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026-08-08</v>
+        <v>2026-08-11</v>
       </c>
       <c r="B5" t="str">
         <v>AMZ-RA-6011</v>
@@ -685,7 +685,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-08-08</v>
+        <v>2026-08-11</v>
       </c>
       <c r="B6" t="str">
         <v>AMZ-RA-6012</v>
@@ -741,7 +741,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-08-08</v>
+        <v>2026-08-11</v>
       </c>
       <c r="B7" t="str">
         <v>AMZ-RA-6013</v>
@@ -864,7 +864,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-08-08</v>
+        <v>2026-08-11</v>
       </c>
       <c r="B2" t="str">
         <v>EBAY-SM-6006</v>
@@ -920,7 +920,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-08-08</v>
+        <v>2026-08-11</v>
       </c>
       <c r="B3" t="str">
         <v>EBAY-SM-6007</v>

--- a/e2e-screenshots/reports-insights-panels/fixtures/VELOCITY_SALES.xlsx
+++ b/e2e-screenshots/reports-insights-panels/fixtures/VELOCITY_SALES.xlsx
@@ -461,7 +461,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-08-11</v>
+        <v>2026-09-05</v>
       </c>
       <c r="B2" t="str">
         <v>AMZ-FM-6001</v>
@@ -517,7 +517,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-08-11</v>
+        <v>2026-09-05</v>
       </c>
       <c r="B3" t="str">
         <v>AMZ-FM-6002</v>
@@ -573,7 +573,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-08-11</v>
+        <v>2026-09-05</v>
       </c>
       <c r="B4" t="str">
         <v>AMZ-RA-6010</v>
@@ -629,7 +629,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026-08-11</v>
+        <v>2026-09-05</v>
       </c>
       <c r="B5" t="str">
         <v>AMZ-RA-6011</v>
@@ -685,7 +685,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-08-11</v>
+        <v>2026-09-05</v>
       </c>
       <c r="B6" t="str">
         <v>AMZ-RA-6012</v>
@@ -741,7 +741,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-08-11</v>
+        <v>2026-09-05</v>
       </c>
       <c r="B7" t="str">
         <v>AMZ-RA-6013</v>
@@ -864,7 +864,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-08-11</v>
+        <v>2026-09-05</v>
       </c>
       <c r="B2" t="str">
         <v>EBAY-SM-6006</v>
@@ -920,7 +920,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-08-11</v>
+        <v>2026-09-05</v>
       </c>
       <c r="B3" t="str">
         <v>EBAY-SM-6007</v>

--- a/e2e-screenshots/reports-insights-panels/fixtures/VELOCITY_SALES.xlsx
+++ b/e2e-screenshots/reports-insights-panels/fixtures/VELOCITY_SALES.xlsx
@@ -461,7 +461,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-09-05</v>
+        <v>2026-09-09</v>
       </c>
       <c r="B2" t="str">
         <v>AMZ-FM-6001</v>
@@ -517,7 +517,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-09-05</v>
+        <v>2026-09-09</v>
       </c>
       <c r="B3" t="str">
         <v>AMZ-FM-6002</v>
@@ -573,7 +573,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-09-05</v>
+        <v>2026-09-09</v>
       </c>
       <c r="B4" t="str">
         <v>AMZ-RA-6010</v>
@@ -629,7 +629,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026-09-05</v>
+        <v>2026-09-09</v>
       </c>
       <c r="B5" t="str">
         <v>AMZ-RA-6011</v>
@@ -685,7 +685,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-09-05</v>
+        <v>2026-09-09</v>
       </c>
       <c r="B6" t="str">
         <v>AMZ-RA-6012</v>
@@ -741,7 +741,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-09-05</v>
+        <v>2026-09-09</v>
       </c>
       <c r="B7" t="str">
         <v>AMZ-RA-6013</v>
@@ -864,7 +864,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-09-05</v>
+        <v>2026-09-09</v>
       </c>
       <c r="B2" t="str">
         <v>EBAY-SM-6006</v>
@@ -920,7 +920,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-09-05</v>
+        <v>2026-09-09</v>
       </c>
       <c r="B3" t="str">
         <v>EBAY-SM-6007</v>
